--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2275,6 +2275,430 @@
       <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113610431</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136552100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Z336 Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>396482</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7063861</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136552100</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136552105</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Z336 Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>396478</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7063840</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136552105</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136551122</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110087</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Z336 Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>396474</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7063838</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136551122</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136552151</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102694</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Z336 Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>396481</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7063859</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136552151</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2719,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110087</v>
+        <v>110090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110090</v>
+        <v>110091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110091</v>
+        <v>110096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>136552100</v>
       </c>
       <c r="B17" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136552105</v>
       </c>
       <c r="B18" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136551122</v>
       </c>
       <c r="B19" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136552151</v>
       </c>
       <c r="B20" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
